--- a/reports/播客监控日报_2026-03-15.xlsx
+++ b/reports/播客监控日报_2026-03-15.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>172749</v>
+        <v>172829</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:06</t>
+          <t>2026-03-15 04:20:18</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>119109</v>
+        <v>119320</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>18761</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:54</t>
+          <t>2026-03-15 04:21:05</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>74904</v>
+        <v>75177</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:08</t>
+          <t>2026-03-15 04:20:19</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>49447</v>
+        <v>49465</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:52</t>
+          <t>2026-03-15 04:21:03</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37421</v>
+        <v>37519</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>战火中的“黑金”——2026 年中东变局与石油投资指南</t>
+          <t>一周富盘 | “养龙虾”爆火刷屏！头部大厂纷纷入局，AI智能体热潮下，基金该怎么布局？</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1:00:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:10</t>
+          <t>2026-03-15 04:20:21</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>26887</v>
+        <v>26886</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:14</t>
+          <t>2026-03-15 04:20:25</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>22724</v>
+        <v>22726</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:50</t>
+          <t>2026-03-15 04:21:01</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20509</v>
+        <v>20510</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:16</t>
+          <t>2026-03-15 04:20:27</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8909</v>
+        <v>8917</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:48</t>
+          <t>2026-03-15 04:20:59</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8425</v>
+        <v>8438</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308.理性看待“全民装虾”：AI狂欢背后的机遇与深思</t>
+          <t>309.全球游客涌向中国春节：一场文化与旅游的双向奔赴</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1099,142 +1099,142 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6:39</t>
+          <t>5:56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:26</t>
+          <t>2026-03-15 04:20:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>茶水间经济学</t>
+          <t>随基漫步 Random Walk</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>易方达基金</t>
+          <t>兴全基金</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6828</v>
+        <v>6833</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
+          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1:42:13</t>
+          <t>55:15</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:36</t>
+          <t>2026-03-15 04:20:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>随基漫步 Random Walk</t>
+          <t>茶水间经济学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>兴全基金</t>
+          <t>易方达基金</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>6813</v>
+        <v>6830</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
+          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55:15</t>
+          <t>1:42:13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:44</t>
+          <t>2026-03-15 04:20:47</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6275</v>
+        <v>6276</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:34</t>
+          <t>2026-03-15 04:20:45</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5382</v>
+        <v>5384</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>514</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:32</t>
+          <t>2026-03-15 04:20:43</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:38</t>
+          <t>2026-03-15 04:20:49</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:40</t>
+          <t>2026-03-15 04:20:51</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:18</t>
+          <t>2026-03-15 04:20:29</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:42</t>
+          <t>2026-03-15 04:20:53</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>346</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:24</t>
+          <t>2026-03-15 04:20:35</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:28</t>
+          <t>2026-03-15 04:20:39</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:12</t>
+          <t>2026-03-15 04:20:23</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:46</t>
+          <t>2026-03-15 04:20:57</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:20</t>
+          <t>2026-03-15 04:20:31</t>
         </is>
       </c>
     </row>
@@ -1924,29 +1924,29 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1:00:18</t>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:22</t>
+          <t>2026-03-15 04:20:33</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 02:30:30</t>
+          <t>2026-03-15 04:20:41</t>
         </is>
       </c>
     </row>
